--- a/artfynd/A 25145-2021 artfynd.xlsx
+++ b/artfynd/A 25145-2021 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 25145-2021 artfynd.xlsx
+++ b/artfynd/A 25145-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY12"/>
+  <dimension ref="A1:AY18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1905,6 +1905,673 @@
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>129763293</v>
+      </c>
+      <c r="B13" t="n">
+        <v>79075</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Vitåskogen, Nb</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>833680</v>
+      </c>
+      <c r="R13" t="n">
+        <v>7332222</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Luleå</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Råneå</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2025-09-02</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>16:13</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2025-09-02</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>16:13</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr">
+        <is>
+          <t>Kalkbarrianerna 2023, 2024, Norrbottens län</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>129763298</v>
+      </c>
+      <c r="B14" t="n">
+        <v>80046</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>388</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Stiftgelélav</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Collema furfuraceum</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Arnold) Du Rietz</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Vitåskogen, Nb</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>833593</v>
+      </c>
+      <c r="R14" t="n">
+        <v>7332210</v>
+      </c>
+      <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Luleå</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Råneå</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2025-09-02</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>16:09</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2025-09-02</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>16:09</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF14" t="inlineStr"/>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr">
+        <is>
+          <t>Kalkbarrianerna 2023, 2024, Norrbottens län</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>129763276</v>
+      </c>
+      <c r="B15" t="n">
+        <v>80046</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>388</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Stiftgelélav</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Collema furfuraceum</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Arnold) Du Rietz</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Vitåskogen, Nb</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>833680</v>
+      </c>
+      <c r="R15" t="n">
+        <v>7332222</v>
+      </c>
+      <c r="S15" t="n">
+        <v>10</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Luleå</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Råneå</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2025-09-02</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>17:19</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2025-09-02</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>17:19</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr">
+        <is>
+          <t>Kalkbarrianerna 2023, 2024, Norrbottens län</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>129763294</v>
+      </c>
+      <c r="B16" t="n">
+        <v>79075</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Vitåskogen, Nb</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>833546</v>
+      </c>
+      <c r="R16" t="n">
+        <v>7332237</v>
+      </c>
+      <c r="S16" t="n">
+        <v>10</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Luleå</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Råneå</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2025-09-02</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>16:07</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2025-09-02</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>16:07</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr">
+        <is>
+          <t>Kalkbarrianerna 2023, 2024, Norrbottens län</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>129763282</v>
+      </c>
+      <c r="B17" t="n">
+        <v>98768</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Vitåskogen, Nb</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>833617</v>
+      </c>
+      <c r="R17" t="n">
+        <v>7332202</v>
+      </c>
+      <c r="S17" t="n">
+        <v>10</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Luleå</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Råneå</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2025-09-02</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>16:11</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2025-09-02</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>16:11</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr">
+        <is>
+          <t>Kalkbarrianerna 2023, 2024, Norrbottens län</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>129763283</v>
+      </c>
+      <c r="B18" t="n">
+        <v>98768</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Vitåskogen, Nb</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>833601</v>
+      </c>
+      <c r="R18" t="n">
+        <v>7332197</v>
+      </c>
+      <c r="S18" t="n">
+        <v>10</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Luleå</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Råneå</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2025-09-02</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>16:10</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2025-09-02</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>16:10</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr">
+        <is>
+          <t>Kalkbarrianerna 2023, 2024, Norrbottens län</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 25145-2021 artfynd.xlsx
+++ b/artfynd/A 25145-2021 artfynd.xlsx
@@ -1910,7 +1910,7 @@
         <v>129763293</v>
       </c>
       <c r="B13" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2021,7 +2021,7 @@
         <v>129763298</v>
       </c>
       <c r="B14" t="n">
-        <v>80046</v>
+        <v>80047</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2133,7 +2133,7 @@
         <v>129763276</v>
       </c>
       <c r="B15" t="n">
-        <v>80046</v>
+        <v>80047</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2244,7 +2244,7 @@
         <v>129763294</v>
       </c>
       <c r="B16" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2355,7 +2355,7 @@
         <v>129763282</v>
       </c>
       <c r="B17" t="n">
-        <v>98768</v>
+        <v>98769</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2466,7 +2466,7 @@
         <v>129763283</v>
       </c>
       <c r="B18" t="n">
-        <v>98768</v>
+        <v>98769</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>

--- a/artfynd/A 25145-2021 artfynd.xlsx
+++ b/artfynd/A 25145-2021 artfynd.xlsx
@@ -1910,7 +1910,7 @@
         <v>129763293</v>
       </c>
       <c r="B13" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2021,7 +2021,7 @@
         <v>129763298</v>
       </c>
       <c r="B14" t="n">
-        <v>80047</v>
+        <v>80052</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2133,7 +2133,7 @@
         <v>129763276</v>
       </c>
       <c r="B15" t="n">
-        <v>80047</v>
+        <v>80052</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2244,7 +2244,7 @@
         <v>129763294</v>
       </c>
       <c r="B16" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2355,7 +2355,7 @@
         <v>129763282</v>
       </c>
       <c r="B17" t="n">
-        <v>98769</v>
+        <v>98774</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2466,7 +2466,7 @@
         <v>129763283</v>
       </c>
       <c r="B18" t="n">
-        <v>98769</v>
+        <v>98774</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>

--- a/artfynd/A 25145-2021 artfynd.xlsx
+++ b/artfynd/A 25145-2021 artfynd.xlsx
@@ -2355,7 +2355,7 @@
         <v>129763282</v>
       </c>
       <c r="B17" t="n">
-        <v>98774</v>
+        <v>98778</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2466,7 +2466,7 @@
         <v>129763283</v>
       </c>
       <c r="B18" t="n">
-        <v>98774</v>
+        <v>98778</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>

--- a/artfynd/A 25145-2021 artfynd.xlsx
+++ b/artfynd/A 25145-2021 artfynd.xlsx
@@ -2355,7 +2355,7 @@
         <v>129763282</v>
       </c>
       <c r="B17" t="n">
-        <v>98778</v>
+        <v>98780</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2466,7 +2466,7 @@
         <v>129763283</v>
       </c>
       <c r="B18" t="n">
-        <v>98778</v>
+        <v>98780</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>

--- a/artfynd/A 25145-2021 artfynd.xlsx
+++ b/artfynd/A 25145-2021 artfynd.xlsx
@@ -2355,7 +2355,7 @@
         <v>129763282</v>
       </c>
       <c r="B17" t="n">
-        <v>98780</v>
+        <v>98790</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2466,7 +2466,7 @@
         <v>129763283</v>
       </c>
       <c r="B18" t="n">
-        <v>98780</v>
+        <v>98790</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>

--- a/artfynd/A 25145-2021 artfynd.xlsx
+++ b/artfynd/A 25145-2021 artfynd.xlsx
@@ -1910,7 +1910,7 @@
         <v>129763293</v>
       </c>
       <c r="B13" t="n">
-        <v>79081</v>
+        <v>79084</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2021,7 +2021,7 @@
         <v>129763298</v>
       </c>
       <c r="B14" t="n">
-        <v>80052</v>
+        <v>80055</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2133,7 +2133,7 @@
         <v>129763276</v>
       </c>
       <c r="B15" t="n">
-        <v>80052</v>
+        <v>80055</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2244,7 +2244,7 @@
         <v>129763294</v>
       </c>
       <c r="B16" t="n">
-        <v>79081</v>
+        <v>79084</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2355,7 +2355,7 @@
         <v>129763282</v>
       </c>
       <c r="B17" t="n">
-        <v>98790</v>
+        <v>98794</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2466,7 +2466,7 @@
         <v>129763283</v>
       </c>
       <c r="B18" t="n">
-        <v>98790</v>
+        <v>98794</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>

--- a/artfynd/A 25145-2021 artfynd.xlsx
+++ b/artfynd/A 25145-2021 artfynd.xlsx
@@ -1910,7 +1910,7 @@
         <v>129763293</v>
       </c>
       <c r="B13" t="n">
-        <v>79084</v>
+        <v>79087</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2021,7 +2021,7 @@
         <v>129763298</v>
       </c>
       <c r="B14" t="n">
-        <v>80055</v>
+        <v>80058</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2133,7 +2133,7 @@
         <v>129763276</v>
       </c>
       <c r="B15" t="n">
-        <v>80055</v>
+        <v>80058</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2244,7 +2244,7 @@
         <v>129763294</v>
       </c>
       <c r="B16" t="n">
-        <v>79084</v>
+        <v>79087</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2355,7 +2355,7 @@
         <v>129763282</v>
       </c>
       <c r="B17" t="n">
-        <v>98794</v>
+        <v>98797</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2466,7 +2466,7 @@
         <v>129763283</v>
       </c>
       <c r="B18" t="n">
-        <v>98794</v>
+        <v>98797</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>

--- a/artfynd/A 25145-2021 artfynd.xlsx
+++ b/artfynd/A 25145-2021 artfynd.xlsx
@@ -1910,7 +1910,7 @@
         <v>129763293</v>
       </c>
       <c r="B13" t="n">
-        <v>79087</v>
+        <v>79088</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2021,7 +2021,7 @@
         <v>129763298</v>
       </c>
       <c r="B14" t="n">
-        <v>80058</v>
+        <v>80059</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2133,7 +2133,7 @@
         <v>129763276</v>
       </c>
       <c r="B15" t="n">
-        <v>80058</v>
+        <v>80059</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2244,7 +2244,7 @@
         <v>129763294</v>
       </c>
       <c r="B16" t="n">
-        <v>79087</v>
+        <v>79088</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2355,7 +2355,7 @@
         <v>129763282</v>
       </c>
       <c r="B17" t="n">
-        <v>98797</v>
+        <v>98798</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2466,7 +2466,7 @@
         <v>129763283</v>
       </c>
       <c r="B18" t="n">
-        <v>98797</v>
+        <v>98798</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>

--- a/artfynd/A 25145-2021 artfynd.xlsx
+++ b/artfynd/A 25145-2021 artfynd.xlsx
@@ -1910,7 +1910,7 @@
         <v>129763293</v>
       </c>
       <c r="B13" t="n">
-        <v>79088</v>
+        <v>79089</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2021,7 +2021,7 @@
         <v>129763298</v>
       </c>
       <c r="B14" t="n">
-        <v>80059</v>
+        <v>80060</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2133,7 +2133,7 @@
         <v>129763276</v>
       </c>
       <c r="B15" t="n">
-        <v>80059</v>
+        <v>80060</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2244,7 +2244,7 @@
         <v>129763294</v>
       </c>
       <c r="B16" t="n">
-        <v>79088</v>
+        <v>79089</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2355,7 +2355,7 @@
         <v>129763282</v>
       </c>
       <c r="B17" t="n">
-        <v>98798</v>
+        <v>98815</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2466,7 +2466,7 @@
         <v>129763283</v>
       </c>
       <c r="B18" t="n">
-        <v>98798</v>
+        <v>98815</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>

--- a/artfynd/A 25145-2021 artfynd.xlsx
+++ b/artfynd/A 25145-2021 artfynd.xlsx
@@ -2105,7 +2105,7 @@
         <v>0</v>
       </c>
       <c r="AE14" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
